--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7FF690-BDA6-4EBA-8E0E-35D2ED1EE3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9CB31F-9EFB-4407-90A4-4DD65805D457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9CB31F-9EFB-4407-90A4-4DD65805D457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A85491D-413A-46CB-A2B0-D6050C3133F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="106">
   <si>
     <t>C1</t>
   </si>
@@ -326,22 +326,10 @@
     <t>high</t>
   </si>
   <si>
-    <t>s1p1v1_d</t>
-  </si>
-  <si>
-    <t>s5p5v5_d</t>
-  </si>
-  <si>
-    <t>ts_annual</t>
-  </si>
-  <si>
     <t>pset_co</t>
   </si>
   <si>
     <t>e 1.5 deg no OS</t>
-  </si>
-  <si>
-    <t>d9d</t>
   </si>
   <si>
     <t>d 1.5 deg OS</t>
@@ -356,9 +344,6 @@
     <t>a 3 deg</t>
   </si>
   <si>
-    <t>c15d</t>
-  </si>
-  <si>
     <t>~Scenmap</t>
   </si>
   <si>
@@ -371,46 +356,7 @@
     <t>priority</t>
   </si>
   <si>
-    <t>ts_012</t>
-  </si>
-  <si>
-    <t>ts_048</t>
-  </si>
-  <si>
-    <t>ts_12t</t>
-  </si>
-  <si>
     <t>bio price multiplier</t>
-  </si>
-  <si>
-    <t>s1v1_d</t>
-  </si>
-  <si>
-    <t>ts_030</t>
-  </si>
-  <si>
-    <t>f2d96</t>
-  </si>
-  <si>
-    <t>ts_096</t>
-  </si>
-  <si>
-    <t>e96</t>
-  </si>
-  <si>
-    <t>ts_072</t>
-  </si>
-  <si>
-    <t>ts_144</t>
-  </si>
-  <si>
-    <t>ts_288</t>
-  </si>
-  <si>
-    <t>x12</t>
-  </si>
-  <si>
-    <t>xAnn</t>
   </si>
   <si>
     <t>Heat growth relative to 2020</t>
@@ -425,9 +371,6 @@
     <t>heat_tfc_twh</t>
   </si>
   <si>
-    <t>HET</t>
-  </si>
-  <si>
     <t>1-8</t>
   </si>
   <si>
@@ -438,6 +381,12 @@
   </si>
   <si>
     <t>heat_buildings_twh</t>
+  </si>
+  <si>
+    <t>het_industry</t>
+  </si>
+  <si>
+    <t>het_buildings</t>
   </si>
   <si>
     <t>IND</t>
@@ -873,7 +822,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$O$17:$U$17</c:f>
+              <c:f>Veda!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -903,30 +852,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$O$14:$U$14</c:f>
+              <c:f>Veda!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>1811.6499999999999</c:v>
+                  <c:v>1812.0100000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2264.5625</c:v>
+                  <c:v>2265.0125000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2826.174</c:v>
+                  <c:v>2826.7356000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3405.9019999999996</c:v>
+                  <c:v>3406.5788000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3949.3969999999999</c:v>
+                  <c:v>3950.1818000000007</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4637.8239999999996</c:v>
+                  <c:v>4638.7456000000011</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5181.3189999999995</c:v>
+                  <c:v>5182.3486000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1161,7 +1110,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$D$17:$J$17</c:f>
+              <c:f>Veda!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1191,7 +1140,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$D$24:$J$24</c:f>
+              <c:f>Veda!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1386,13 +1335,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>481012</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>250032</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5975,7 +5924,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G1" s="16" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6001,24 +5950,24 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6033,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E9" s="14">
         <v>0</v>
@@ -6052,7 +6001,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E10" s="14">
         <v>100</v>
@@ -6071,7 +6020,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E11" s="14">
         <v>200</v>
@@ -6090,7 +6039,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E12" s="14">
         <v>300</v>
@@ -6196,7 +6145,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH78"/>
+  <dimension ref="A1:AH50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -6217,13 +6166,13 @@
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>25</v>
@@ -6242,7 +6191,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>7</v>
@@ -6280,30 +6229,18 @@
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="AH8" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="N9" t="s">
         <v>4</v>
       </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE9" s="10">
-        <v>1</v>
-      </c>
       <c r="AF9" t="s">
         <v>0</v>
       </c>
       <c r="AG9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AH9" s="12">
         <v>5</v>
@@ -6313,23 +6250,11 @@
       <c r="N10" s="1">
         <v>2022</v>
       </c>
-      <c r="AB10">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE10" s="10">
-        <v>1</v>
-      </c>
       <c r="AF10" t="s">
         <v>2</v>
       </c>
       <c r="AG10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AH10" s="12">
         <v>4</v>
@@ -6337,30 +6262,17 @@
     </row>
     <row r="11" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N11" s="17">
-        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O28-O29</f>
-        <v>1811.6499999999999</v>
+        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
+        <v>1812.0100000000002</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AB11">
-        <v>3</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD11" t="str">
-        <f>AC11</f>
-        <v>ts_012</v>
-      </c>
-      <c r="AE11" s="10">
-        <v>1</v>
-      </c>
       <c r="AF11" t="s">
         <v>5</v>
       </c>
       <c r="AG11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AH11" s="12">
         <v>3</v>
@@ -6368,1464 +6280,1077 @@
     </row>
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="N12" s="17">
-        <f>SUMIFS(iea_data!J3:J9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>4</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD12" t="str">
-        <f t="shared" ref="AD12:AD16" si="0">AC12</f>
-        <v>ts_030</v>
-      </c>
-      <c r="AE12" s="10">
-        <v>1</v>
+        <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>0</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
       </c>
       <c r="AG12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AH12" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="AB13">
-        <v>5</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD13" t="str">
-        <f t="shared" si="0"/>
-        <v>ts_048</v>
-      </c>
-      <c r="AE13" s="10">
-        <v>1</v>
+    <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N13" s="17">
+        <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>0</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
       </c>
       <c r="AG13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AH13" s="12">
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+    <row r="14" spans="1:34" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="3" t="str">
+      <c r="C15" s="3" t="str">
         <f>VLOOKUP(controller!$D$5,$I$3:$J$5,2,FALSE)</f>
         <v>C4</v>
       </c>
-      <c r="D14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="D15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.25</v>
       </c>
-      <c r="F14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="F15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.56</v>
       </c>
-      <c r="G14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="G15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>1.88</v>
       </c>
-      <c r="H14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="H15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>2.1800000000000002</v>
       </c>
-      <c r="I14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="I15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>2.56</v>
       </c>
-      <c r="J14" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B14,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="J15" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>2.86</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O15" s="8">
         <f>N11</f>
-        <v>1811.6499999999999</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" ref="P14:U14" si="1">$N$11*E14</f>
-        <v>2264.5625</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="1"/>
-        <v>2826.174</v>
-      </c>
-      <c r="R14" s="8">
-        <f t="shared" si="1"/>
-        <v>3405.9019999999996</v>
-      </c>
-      <c r="S14" s="8">
-        <f t="shared" si="1"/>
-        <v>3949.3969999999999</v>
-      </c>
-      <c r="T14" s="8">
-        <f t="shared" si="1"/>
-        <v>4637.8239999999996</v>
-      </c>
-      <c r="U14" s="8">
-        <f t="shared" si="1"/>
-        <v>5181.3189999999995</v>
-      </c>
-      <c r="AB14">
-        <v>6</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>106</v>
-      </c>
-      <c r="AD14" t="str">
+        <v>1812.0100000000002</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
+        <v>2265.0125000000003</v>
+      </c>
+      <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>ts_072</v>
-      </c>
-      <c r="AE14" s="10">
-        <f>AE9+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B15,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>7</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>107</v>
-      </c>
-      <c r="AD15" t="str">
+        <v>2826.7356000000004</v>
+      </c>
+      <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>ts_144</v>
-      </c>
-      <c r="AE15" s="10">
-        <f t="shared" ref="AE15:AE78" si="2">AE10+1</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N16" s="5" t="str">
+        <v>3406.5788000000002</v>
+      </c>
+      <c r="S15" s="8">
+        <f t="shared" si="0"/>
+        <v>3950.1818000000007</v>
+      </c>
+      <c r="T15" s="8">
+        <f t="shared" si="0"/>
+        <v>4638.7456000000011</v>
+      </c>
+      <c r="U15" s="8">
+        <f t="shared" si="0"/>
+        <v>5182.3486000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B16,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=IND</v>
       </c>
-      <c r="AB16">
-        <v>8</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD16" t="str">
-        <f t="shared" si="0"/>
-        <v>ts_288</v>
-      </c>
-      <c r="AE16" s="10">
+    </row>
+    <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D18" s="7">
+        <v>2020</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" ref="E18:J18" si="1">P18</f>
+        <v>2025</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="1"/>
+        <v>2030</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="1"/>
+        <v>2035</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="1"/>
+        <v>2040</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="1"/>
+        <v>2045</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="1"/>
+        <v>2050</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="4">
+        <v>2022</v>
+      </c>
+      <c r="P18" s="4">
+        <v>2025</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>2030</v>
+      </c>
+      <c r="R18" s="4">
+        <v>2035</v>
+      </c>
+      <c r="S18" s="4">
+        <v>2040</v>
+      </c>
+      <c r="T18" s="4">
+        <v>2045</v>
+      </c>
+      <c r="U18" s="4">
+        <v>2050</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.01</v>
+      </c>
+      <c r="J19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.01</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="6">
+        <f t="shared" ref="O19:U21" si="2">D19*O$15</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:31" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="7">
-        <v>2020</v>
-      </c>
-      <c r="E17" s="7">
-        <f t="shared" ref="E17:J17" si="3">P17</f>
-        <v>2025</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="3"/>
-        <v>2030</v>
-      </c>
-      <c r="G17" s="7">
-        <f t="shared" si="3"/>
-        <v>2035</v>
-      </c>
-      <c r="H17" s="7">
-        <f t="shared" si="3"/>
-        <v>2040</v>
-      </c>
-      <c r="I17" s="7">
-        <f t="shared" si="3"/>
-        <v>2045</v>
-      </c>
-      <c r="J17" s="7">
-        <f t="shared" si="3"/>
-        <v>2050</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="O17" s="4">
-        <v>2022</v>
-      </c>
-      <c r="P17" s="4">
-        <v>2025</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>2030</v>
-      </c>
-      <c r="R17" s="4">
-        <v>2035</v>
-      </c>
-      <c r="S17" s="4">
-        <v>2040</v>
-      </c>
-      <c r="T17" s="4">
-        <v>2045</v>
-      </c>
-      <c r="U17" s="4">
-        <v>2050</v>
-      </c>
-      <c r="V17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB17">
-        <v>9</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.01</v>
-      </c>
-      <c r="J18" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B18,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.01</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="O18" s="6">
-        <f t="shared" ref="O18:U20" si="4">D18*O$14</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="6">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="6">
-        <f t="shared" si="4"/>
-        <v>46.378239999999998</v>
-      </c>
-      <c r="U18" s="6">
-        <f t="shared" si="4"/>
-        <v>51.813189999999999</v>
-      </c>
-      <c r="V18" t="s">
-        <v>16</v>
-      </c>
-      <c r="X18" s="2"/>
-      <c r="AB18">
-        <v>10</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>105</v>
-      </c>
-      <c r="AE18" s="10">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.47</v>
-      </c>
-      <c r="E19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.46</v>
-      </c>
-      <c r="F19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.41</v>
-      </c>
-      <c r="G19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.44</v>
-      </c>
-      <c r="H19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.42</v>
-      </c>
-      <c r="I19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.42</v>
-      </c>
-      <c r="J19" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B19,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.43</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O19" s="6">
-        <f t="shared" si="4"/>
-        <v>851.4754999999999</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" si="4"/>
-        <v>1041.69875</v>
-      </c>
-      <c r="Q19" s="6">
-        <f t="shared" si="4"/>
-        <v>1158.7313399999998</v>
-      </c>
-      <c r="R19" s="6">
-        <f t="shared" si="4"/>
-        <v>1498.5968799999998</v>
+        <v>0</v>
       </c>
       <c r="S19" s="6">
-        <f t="shared" si="4"/>
-        <v>1658.7467399999998</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="T19" s="6">
-        <f t="shared" si="4"/>
-        <v>1947.8860799999998</v>
+        <f t="shared" si="2"/>
+        <v>46.387456000000014</v>
       </c>
       <c r="U19" s="6">
-        <f t="shared" si="4"/>
-        <v>2227.9671699999999</v>
+        <f t="shared" si="2"/>
+        <v>51.823486000000003</v>
       </c>
       <c r="V19" t="s">
         <v>16</v>
       </c>
-      <c r="AB19">
-        <v>11</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE19" s="10">
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="E20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="F20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.41</v>
+      </c>
+      <c r="G20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.44</v>
+      </c>
+      <c r="H20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.42</v>
+      </c>
+      <c r="I20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.42</v>
+      </c>
+      <c r="J20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.43</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.4</v>
-      </c>
-      <c r="E20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.46</v>
-      </c>
-      <c r="F20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.46</v>
-      </c>
-      <c r="G20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.46</v>
-      </c>
-      <c r="H20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.48</v>
-      </c>
-      <c r="I20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.48</v>
-      </c>
-      <c r="J20" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B20,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.47</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="6">
-        <f t="shared" si="4"/>
-        <v>724.66</v>
+        <v>851.64470000000006</v>
       </c>
       <c r="P20" s="6">
-        <f t="shared" si="4"/>
-        <v>1041.69875</v>
+        <f t="shared" si="2"/>
+        <v>1041.9057500000001</v>
       </c>
       <c r="Q20" s="6">
-        <f t="shared" si="4"/>
-        <v>1300.0400400000001</v>
+        <f t="shared" si="2"/>
+        <v>1158.9615960000001</v>
       </c>
       <c r="R20" s="6">
-        <f t="shared" si="4"/>
-        <v>1566.7149199999999</v>
+        <f t="shared" si="2"/>
+        <v>1498.8946720000001</v>
       </c>
       <c r="S20" s="6">
-        <f t="shared" si="4"/>
-        <v>1895.71056</v>
+        <f t="shared" si="2"/>
+        <v>1659.0763560000003</v>
       </c>
       <c r="T20" s="6">
-        <f t="shared" si="4"/>
-        <v>2226.1555199999998</v>
+        <f t="shared" si="2"/>
+        <v>1948.2731520000004</v>
       </c>
       <c r="U20" s="6">
-        <f t="shared" si="4"/>
-        <v>2435.2199299999997</v>
+        <f t="shared" si="2"/>
+        <v>2228.4098979999999</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
       </c>
-      <c r="AB20">
-        <v>12</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>92</v>
-      </c>
-      <c r="AE20" s="10">
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.4</v>
+      </c>
+      <c r="E21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="F21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="G21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="H21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.48</v>
+      </c>
+      <c r="I21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.48</v>
+      </c>
+      <c r="J21" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.02</v>
-      </c>
-      <c r="E21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.02</v>
-      </c>
-      <c r="F21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.02</v>
-      </c>
-      <c r="G21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.03</v>
-      </c>
-      <c r="H21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.04</v>
-      </c>
-      <c r="I21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.04</v>
-      </c>
-      <c r="J21" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$14,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B21,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.05</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" s="6">
-        <f>D21*O$14</f>
-        <v>36.232999999999997</v>
+        <v>724.80400000000009</v>
       </c>
       <c r="P21" s="6">
-        <f t="shared" ref="P21:U21" si="5">O21</f>
-        <v>36.232999999999997</v>
+        <f t="shared" si="2"/>
+        <v>1041.9057500000001</v>
       </c>
       <c r="Q21" s="6">
-        <f t="shared" si="5"/>
-        <v>36.232999999999997</v>
+        <f t="shared" si="2"/>
+        <v>1300.2983760000002</v>
       </c>
       <c r="R21" s="6">
-        <f t="shared" si="5"/>
-        <v>36.232999999999997</v>
+        <f t="shared" si="2"/>
+        <v>1567.0262480000001</v>
       </c>
       <c r="S21" s="6">
-        <f t="shared" si="5"/>
-        <v>36.232999999999997</v>
+        <f t="shared" si="2"/>
+        <v>1896.0872640000002</v>
       </c>
       <c r="T21" s="6">
-        <f t="shared" si="5"/>
-        <v>36.232999999999997</v>
+        <f t="shared" si="2"/>
+        <v>2226.5978880000002</v>
       </c>
       <c r="U21" s="6">
-        <f t="shared" si="5"/>
-        <v>36.232999999999997</v>
+        <f t="shared" si="2"/>
+        <v>2435.7038419999999</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE21" s="10">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:31" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="F22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.03</v>
+      </c>
+      <c r="H22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.04</v>
+      </c>
+      <c r="I22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.04</v>
+      </c>
+      <c r="J22" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$15,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B22,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.05</v>
+      </c>
       <c r="N22" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O22" s="6">
-        <f t="shared" ref="O22:U22" si="6">O14-SUM(O19:O21)</f>
-        <v>199.28150000000005</v>
+        <f>D22*O$15</f>
+        <v>36.240200000000009</v>
       </c>
       <c r="P22" s="6">
-        <f t="shared" si="6"/>
-        <v>144.93199999999979</v>
+        <f t="shared" ref="P22:U22" si="3">O22</f>
+        <v>36.240200000000009</v>
       </c>
       <c r="Q22" s="6">
-        <f t="shared" si="6"/>
-        <v>331.16961999999967</v>
+        <f t="shared" si="3"/>
+        <v>36.240200000000009</v>
       </c>
       <c r="R22" s="6">
-        <f t="shared" si="6"/>
-        <v>304.35719999999992</v>
+        <f t="shared" si="3"/>
+        <v>36.240200000000009</v>
       </c>
       <c r="S22" s="6">
-        <f t="shared" si="6"/>
-        <v>358.70669999999973</v>
+        <f t="shared" si="3"/>
+        <v>36.240200000000009</v>
       </c>
       <c r="T22" s="6">
-        <f t="shared" si="6"/>
-        <v>427.54939999999988</v>
+        <f t="shared" si="3"/>
+        <v>36.240200000000009</v>
       </c>
       <c r="U22" s="6">
-        <f t="shared" si="6"/>
-        <v>481.89890000000014</v>
+        <f t="shared" si="3"/>
+        <v>36.240200000000009</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
       </c>
-      <c r="AE22" s="10">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="N23" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="O23" s="19">
+      <c r="X22" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="N23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
+        <v>199.32110000000011</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="4"/>
+        <v>144.96079999999984</v>
+      </c>
+      <c r="Q23" s="6">
+        <f t="shared" si="4"/>
+        <v>331.23542799999996</v>
+      </c>
+      <c r="R23" s="6">
+        <f t="shared" si="4"/>
+        <v>304.41767999999956</v>
+      </c>
+      <c r="S23" s="6">
+        <f t="shared" si="4"/>
+        <v>358.7779800000003</v>
+      </c>
+      <c r="T23" s="6">
+        <f t="shared" si="4"/>
+        <v>427.63436000000002</v>
+      </c>
+      <c r="U23" s="6">
+        <f t="shared" si="4"/>
+        <v>481.99466000000029</v>
+      </c>
+      <c r="V23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="N24" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="O24" s="19">
         <f>N12</f>
         <v>0</v>
       </c>
-      <c r="P23" s="20">
-        <f>$N$12*E15</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="20">
-        <f>$N$12*F15</f>
-        <v>0</v>
-      </c>
-      <c r="R23" s="20">
-        <f t="shared" ref="R23:U23" si="7">$N$12*G15</f>
-        <v>0</v>
-      </c>
-      <c r="S23" s="20">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T23" s="20">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="20">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="18" t="s">
+      <c r="P24" s="20">
+        <f>$N$12*E16</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="20">
+        <f>$N$12*F16</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="20">
+        <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="AE23" s="10">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:31" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="10" t="s">
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="N25" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="O25" s="19">
+        <f>N13</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="20">
+        <f>$N$13*E16</f>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="20">
+        <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="20">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="20">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="20">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="20">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C26" s="3" t="str">
         <f>VLOOKUP(controller!E5,$F$3:$G$6,2,FALSE)</f>
         <v>C3</v>
       </c>
-      <c r="D24" s="8">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="D26" s="8">
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>47.87</v>
       </c>
-      <c r="G24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="G26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>86.21</v>
       </c>
-      <c r="H24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="H26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>123.26</v>
       </c>
-      <c r="I24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="I26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>172.36</v>
       </c>
-      <c r="J24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$24,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B24,ar6_r10!$B$2:$B$99999,$A$2)</f>
+      <c r="J26" s="8">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$C$26,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B26,ar6_r10!$B$2:$B$99999,$A$2)</f>
         <v>209.45</v>
       </c>
-      <c r="N24" s="21" t="s">
+      <c r="N26" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="23">
-        <f>F24/1000</f>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="23">
+        <f>F26/1000</f>
         <v>4.7869999999999996E-2</v>
       </c>
-      <c r="R24" s="23">
-        <f>G24/1000</f>
+      <c r="R26" s="23">
+        <f>G26/1000</f>
         <v>8.6209999999999995E-2</v>
       </c>
-      <c r="S24" s="23">
-        <f>H24/1000</f>
+      <c r="S26" s="23">
+        <f>H26/1000</f>
         <v>0.12326000000000001</v>
       </c>
-      <c r="T24" s="23">
-        <f>I24/1000</f>
+      <c r="T26" s="23">
+        <f>I26/1000</f>
         <v>0.17236000000000001</v>
       </c>
-      <c r="U24" s="23">
-        <f>J24/1000</f>
+      <c r="U26" s="23">
+        <f>J26/1000</f>
         <v>0.20945</v>
       </c>
-      <c r="V24" s="24" t="s">
+      <c r="V26" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AE24" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="2:31" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="AE25" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="2:31" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="N26" s="5" t="str">
+    </row>
+    <row r="27" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=IND</v>
       </c>
-      <c r="AE26" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="2:31" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="N27" s="4" t="s">
+    </row>
+    <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O27" s="4">
-        <f t="shared" ref="O27:U27" si="8">O17</f>
+      <c r="O29" s="4">
+        <f t="shared" ref="O29:U29" si="7">O18</f>
         <v>2022</v>
       </c>
-      <c r="P27" s="4">
-        <f t="shared" si="8"/>
+      <c r="P29" s="4">
+        <f t="shared" si="7"/>
         <v>2025</v>
       </c>
-      <c r="Q27" s="4">
-        <f t="shared" si="8"/>
+      <c r="Q29" s="4">
+        <f t="shared" si="7"/>
         <v>2030</v>
       </c>
-      <c r="R27" s="4">
+      <c r="R29" s="4">
+        <f t="shared" si="7"/>
+        <v>2035</v>
+      </c>
+      <c r="S29" s="4">
+        <f t="shared" si="7"/>
+        <v>2040</v>
+      </c>
+      <c r="T29" s="4">
+        <f t="shared" si="7"/>
+        <v>2045</v>
+      </c>
+      <c r="U29" s="4">
+        <f t="shared" si="7"/>
+        <v>2050</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="W29" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L30" s="3">
+        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>7.64</v>
+      </c>
+      <c r="N30" t="s">
+        <v>30</v>
+      </c>
+      <c r="O30" s="3">
+        <f>L30</f>
+        <v>7.64</v>
+      </c>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" t="s">
+        <v>31</v>
+      </c>
+      <c r="W30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="3">
+        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
+        <v>13.79</v>
+      </c>
+      <c r="N31" t="s">
+        <v>33</v>
+      </c>
+      <c r="O31" s="3">
+        <f>ABS(L31)</f>
+        <v>13.79</v>
+      </c>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" t="s">
+        <v>31</v>
+      </c>
+      <c r="W31" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="F39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.21</v>
+      </c>
+      <c r="G39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="H39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.36</v>
+      </c>
+      <c r="I39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.4</v>
+      </c>
+      <c r="J39" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.07</v>
+      </c>
+      <c r="F40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.17</v>
+      </c>
+      <c r="G40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.21</v>
+      </c>
+      <c r="H40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.37</v>
+      </c>
+      <c r="I40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.33</v>
+      </c>
+      <c r="J40" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.43</v>
+      </c>
+      <c r="F41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.58</v>
+      </c>
+      <c r="G41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.53</v>
+      </c>
+      <c r="H41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.74</v>
+      </c>
+      <c r="I41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.94</v>
+      </c>
+      <c r="J41" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B41,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,D$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="E42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,E$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.05</v>
+      </c>
+      <c r="F42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,F$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.06</v>
+      </c>
+      <c r="G42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,G$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1.04</v>
+      </c>
+      <c r="H42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,H$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="I42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,I$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.95</v>
+      </c>
+      <c r="J42" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$38,ar6_r10!$C$2:$C$99999,J$18,ar6_r10!$M$2:$M$99999,$B42,ar6_r10!$B$2:$B$99999,$A$2)</f>
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="5" t="str">
+        <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
+        <v>~TFM_INS-TS: region=IND; attribute=flo_cost;pset_pn=-IMP*Z</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46">
+        <v>2022</v>
+      </c>
+      <c r="E46">
+        <f>E18</f>
+        <v>2025</v>
+      </c>
+      <c r="F46">
+        <f t="shared" ref="F46:J46" si="8">F18</f>
+        <v>2030</v>
+      </c>
+      <c r="G46">
         <f t="shared" si="8"/>
         <v>2035</v>
       </c>
-      <c r="S27" s="4">
+      <c r="H46">
         <f t="shared" si="8"/>
         <v>2040</v>
       </c>
-      <c r="T27" s="4">
+      <c r="I46">
         <f t="shared" si="8"/>
         <v>2045</v>
       </c>
-      <c r="U27" s="4">
+      <c r="J46">
         <f t="shared" si="8"/>
         <v>2050</v>
       </c>
-      <c r="V27" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="W27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE27" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="2:31" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L28" s="3">
-        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>7.84</v>
-      </c>
-      <c r="N28" t="s">
-        <v>30</v>
-      </c>
-      <c r="O28" s="3">
-        <f>L28</f>
-        <v>7.84</v>
-      </c>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" t="s">
-        <v>31</v>
-      </c>
-      <c r="W28" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE28" s="10">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="2:31" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L29" s="3">
-        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>-10.25</v>
-      </c>
-      <c r="N29" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" s="3">
-        <f>-1*L29</f>
-        <v>10.25</v>
-      </c>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" t="s">
-        <v>31</v>
-      </c>
-      <c r="W29" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE29" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:31" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="AE30" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AE31" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AE32" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AE33" s="10">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AE34" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AE35" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE36" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="F37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.21</v>
-      </c>
-      <c r="G37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="H37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.36</v>
-      </c>
-      <c r="I37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.4</v>
-      </c>
-      <c r="J37" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B37,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.44</v>
-      </c>
-      <c r="AE37" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.07</v>
-      </c>
-      <c r="F38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.17</v>
-      </c>
-      <c r="G38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.21</v>
-      </c>
-      <c r="H38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.37</v>
-      </c>
-      <c r="I38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.33</v>
-      </c>
-      <c r="J38" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B38,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.52</v>
-      </c>
-      <c r="AE38" s="10">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.43</v>
-      </c>
-      <c r="F39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.58</v>
-      </c>
-      <c r="G39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.53</v>
-      </c>
-      <c r="H39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.74</v>
-      </c>
-      <c r="I39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.94</v>
-      </c>
-      <c r="J39" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B39,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="AE39" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="D40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,D$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="E40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,E$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.05</v>
-      </c>
-      <c r="F40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,F$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.06</v>
-      </c>
-      <c r="G40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,G$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1.04</v>
-      </c>
-      <c r="H40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,H$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>1</v>
-      </c>
-      <c r="I40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,I$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.95</v>
-      </c>
-      <c r="J40" s="11">
-        <f>SUMIFS(ar6_r10!$F$2:$F$99999,ar6_r10!$A$2:$A$99999,$B$36,ar6_r10!$C$2:$C$99999,J$17,ar6_r10!$M$2:$M$99999,$B40,ar6_r10!$B$2:$B$99999,$A$2)</f>
-        <v>0.93</v>
-      </c>
-      <c r="AE40" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AE41" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="AE42" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="5" t="str">
-        <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=IND; attribute=flo_cost;pset_pn=-IMP*Z</v>
-      </c>
-      <c r="AE43" s="10">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44">
-        <v>2022</v>
-      </c>
-      <c r="E44">
-        <f>E17</f>
-        <v>2025</v>
-      </c>
-      <c r="F44">
-        <f t="shared" ref="F44:J44" si="9">F17</f>
-        <v>2030</v>
-      </c>
-      <c r="G44">
+      <c r="M46" t="s">
+        <v>80</v>
+      </c>
+      <c r="N46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" t="str">
+        <f>B47</f>
+        <v>Gas</v>
+      </c>
+      <c r="D47">
+        <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
+        <v>36</v>
+      </c>
+      <c r="E47">
         <f t="shared" si="9"/>
-        <v>2035</v>
-      </c>
-      <c r="H44">
+        <v>39.96</v>
+      </c>
+      <c r="F47">
         <f t="shared" si="9"/>
-        <v>2040</v>
-      </c>
-      <c r="I44">
+        <v>43.56</v>
+      </c>
+      <c r="G47">
         <f t="shared" si="9"/>
-        <v>2045</v>
-      </c>
-      <c r="J44">
+        <v>41.76</v>
+      </c>
+      <c r="H47">
         <f t="shared" si="9"/>
-        <v>2050</v>
-      </c>
-      <c r="M44" t="s">
-        <v>80</v>
-      </c>
-      <c r="N44" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE44" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" t="str">
-        <f>B45</f>
-        <v>Gas</v>
-      </c>
-      <c r="D45">
-        <f t="shared" ref="D45:J48" si="10">AVERAGE($M45:$N45)*D37</f>
-        <v>36</v>
-      </c>
-      <c r="E45">
+        <v>48.96</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="9"/>
+        <v>50.4</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="9"/>
+        <v>51.839999999999996</v>
+      </c>
+      <c r="M47">
+        <f>HLOOKUP($B47&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>30.9</v>
+      </c>
+      <c r="N47">
+        <f>HLOOKUP($B47&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" ref="C48:C50" si="10">B48</f>
+        <v>Coal</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="9"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="9"/>
+        <v>10.486000000000001</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="9"/>
+        <v>11.465999999999999</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="9"/>
+        <v>11.858000000000001</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="9"/>
+        <v>13.426000000000002</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="9"/>
+        <v>13.034000000000002</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="9"/>
+        <v>14.896000000000001</v>
+      </c>
+      <c r="M48">
+        <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>8.6</v>
+      </c>
+      <c r="N48">
+        <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" t="str">
         <f t="shared" si="10"/>
-        <v>39.96</v>
-      </c>
-      <c r="F45">
+        <v>Oil</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="9"/>
+        <v>50</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="9"/>
+        <v>71.5</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="9"/>
+        <v>79</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="9"/>
+        <v>76.5</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="9"/>
+        <v>87</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="9"/>
+        <v>97</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="9"/>
+        <v>110.00000000000001</v>
+      </c>
+      <c r="M49">
+        <f>HLOOKUP($B49&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>45</v>
+      </c>
+      <c r="N49">
+        <f>HLOOKUP($B49&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="str">
         <f t="shared" si="10"/>
-        <v>43.56</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="10"/>
-        <v>41.76</v>
-      </c>
-      <c r="H45">
-        <f t="shared" si="10"/>
-        <v>48.96</v>
-      </c>
-      <c r="I45">
-        <f t="shared" si="10"/>
-        <v>50.4</v>
-      </c>
-      <c r="J45">
-        <f t="shared" si="10"/>
-        <v>51.839999999999996</v>
-      </c>
-      <c r="M45">
-        <f>HLOOKUP($B45&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>30.9</v>
-      </c>
-      <c r="N45">
-        <f>HLOOKUP($B45&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>41.1</v>
-      </c>
-      <c r="AE45" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" t="str">
-        <f t="shared" ref="C46:C48" si="11">B46</f>
-        <v>Coal</v>
-      </c>
-      <c r="D46">
-        <f t="shared" si="10"/>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="E46">
-        <f t="shared" si="10"/>
-        <v>10.486000000000001</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="10"/>
-        <v>11.465999999999999</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="10"/>
-        <v>11.858000000000001</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="10"/>
-        <v>13.426000000000002</v>
-      </c>
-      <c r="I46">
-        <f t="shared" si="10"/>
-        <v>13.034000000000002</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="10"/>
-        <v>14.896000000000001</v>
-      </c>
-      <c r="M46">
-        <f>HLOOKUP($B46&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>8.6</v>
-      </c>
-      <c r="N46">
-        <f>HLOOKUP($B46&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>11</v>
-      </c>
-      <c r="AE46" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" t="str">
-        <f t="shared" si="11"/>
-        <v>Oil</v>
-      </c>
-      <c r="D47">
-        <f t="shared" si="10"/>
-        <v>50</v>
-      </c>
-      <c r="E47">
-        <f t="shared" si="10"/>
-        <v>71.5</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="10"/>
-        <v>79</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="10"/>
-        <v>76.5</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="10"/>
-        <v>87</v>
-      </c>
-      <c r="I47">
-        <f t="shared" si="10"/>
-        <v>97</v>
-      </c>
-      <c r="J47">
-        <f t="shared" si="10"/>
-        <v>110.00000000000001</v>
-      </c>
-      <c r="M47">
-        <f>HLOOKUP($B47&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>45</v>
-      </c>
-      <c r="N47">
-        <f>HLOOKUP($B47&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>55</v>
-      </c>
-      <c r="AE47" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" t="str">
-        <f t="shared" si="11"/>
         <v>Bioenergy</v>
       </c>
-      <c r="D48">
-        <f t="shared" si="10"/>
+      <c r="D50">
+        <f t="shared" si="9"/>
         <v>18.5</v>
       </c>
-      <c r="J48">
-        <f>VLOOKUP($C$14,$AF$9:$AH$15,3,FALSE)*D48</f>
+      <c r="J50">
+        <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
         <v>55.5</v>
       </c>
-      <c r="M48">
-        <f>HLOOKUP($B48&amp;"_"&amp;M$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+      <c r="M50">
+        <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
         <v>15</v>
       </c>
-      <c r="N48">
-        <f>HLOOKUP($B48&amp;"_"&amp;N$44,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
+      <c r="N50">
+        <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
         <v>22</v>
-      </c>
-      <c r="AE48" s="10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE49" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE50" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE51" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE52" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE53" s="10">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE54" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE55" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE56" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE57" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE58" s="10">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE59" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE60" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE61" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE62" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE63" s="10">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE64" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE65" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="66" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE66" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE67" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE68" s="10">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE69" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE70" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="71" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE71" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE72" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE73" s="10">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE74" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE75" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE76" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE77" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="78" spans="31:31" x14ac:dyDescent="0.25">
-      <c r="AE78" s="10">
-        <f t="shared" si="2"/>
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -7887,7 +7412,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B11">
         <v>30.9</v>
@@ -7914,7 +7439,7 @@
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -7925,7 +7450,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.5703125" customWidth="1"/>
@@ -7974,45 +7499,45 @@
         <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="K10" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="L10" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="M10" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B11">
-        <v>2000</v>
+        <v>2015</v>
       </c>
       <c r="C11">
-        <v>353.17</v>
+        <v>680.03</v>
       </c>
       <c r="D11">
-        <v>183.05</v>
+        <v>497.88</v>
       </c>
       <c r="E11">
-        <v>8.2100000000000009</v>
+        <v>16.59</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="G11">
-        <v>1.5</v>
+        <v>5.24</v>
       </c>
       <c r="H11">
-        <v>-0.2</v>
+        <v>5.15</v>
       </c>
       <c r="I11">
-        <v>561.05999999999995</v>
+        <v>1357.62</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -8029,31 +7554,31 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B12">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="C12">
-        <v>365.24</v>
+        <v>704.65</v>
       </c>
       <c r="D12">
-        <v>185.84</v>
+        <v>536.57000000000005</v>
       </c>
       <c r="E12">
-        <v>8.11</v>
+        <v>15.68</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="G12">
-        <v>1.52</v>
+        <v>5.62</v>
       </c>
       <c r="H12">
-        <v>-0.23</v>
+        <v>6.71</v>
       </c>
       <c r="I12">
-        <v>579.62</v>
+        <v>1432.74</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -8070,31 +7595,31 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B13">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="C13">
-        <v>373.25</v>
+        <v>748.88</v>
       </c>
       <c r="D13">
-        <v>197.43</v>
+        <v>566.27</v>
       </c>
       <c r="E13">
-        <v>8.8000000000000007</v>
+        <v>17.43</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="G13">
-        <v>1.52</v>
+        <v>5.07</v>
       </c>
       <c r="H13">
-        <v>-0.17</v>
+        <v>7.2</v>
       </c>
       <c r="I13">
-        <v>602.77</v>
+        <v>1509.93</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -8111,31 +7636,31 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B14">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="C14">
-        <v>398.6</v>
+        <v>831.73</v>
       </c>
       <c r="D14">
-        <v>209.74</v>
+        <v>599.55999999999995</v>
       </c>
       <c r="E14">
-        <v>9.2100000000000009</v>
+        <v>18.84</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="G14">
-        <v>1.75</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="H14">
-        <v>-0.06</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="I14">
-        <v>640.35</v>
+        <v>1608.64</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -8152,31 +7677,31 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B15">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="C15">
-        <v>420.06</v>
+        <v>869.08</v>
       </c>
       <c r="D15">
-        <v>219.17</v>
+        <v>625.71</v>
       </c>
       <c r="E15">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="F15">
+        <v>0.38</v>
+      </c>
+      <c r="G15">
+        <v>6.35</v>
+      </c>
+      <c r="H15">
         <v>9.49</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>1.74</v>
-      </c>
-      <c r="H15">
-        <v>-0.04</v>
-      </c>
       <c r="I15">
-        <v>675.52</v>
+        <v>1646.41</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -8193,31 +7718,31 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B16">
-        <v>2005</v>
+        <v>2020</v>
       </c>
       <c r="C16">
-        <v>440.21</v>
+        <v>756.88</v>
       </c>
       <c r="D16">
-        <v>233.64</v>
+        <v>638.6</v>
       </c>
       <c r="E16">
-        <v>9.94</v>
+        <v>14.67</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="G16">
-        <v>1.76</v>
+        <v>9.5500000000000007</v>
       </c>
       <c r="H16">
-        <v>-0.21</v>
+        <v>9.57</v>
       </c>
       <c r="I16">
-        <v>708.4</v>
+        <v>1536.67</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -8234,31 +7759,31 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B17">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="C17">
-        <v>473.33</v>
+        <v>787.59</v>
       </c>
       <c r="D17">
-        <v>260.14</v>
+        <v>664.7</v>
       </c>
       <c r="E17">
-        <v>10.8</v>
+        <v>21.94</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="G17">
-        <v>2.96</v>
+        <v>7.97</v>
       </c>
       <c r="H17">
-        <v>-0.22</v>
+        <v>9.25</v>
       </c>
       <c r="I17">
-        <v>767.3</v>
+        <v>1636.57</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -8275,31 +7800,31 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B18">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="C18">
-        <v>508.87</v>
+        <v>898.12</v>
       </c>
       <c r="D18">
-        <v>274.29000000000002</v>
+        <v>713.08</v>
       </c>
       <c r="E18">
-        <v>11.11</v>
+        <v>30.03</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="G18">
-        <v>5.23</v>
+        <v>7.64</v>
       </c>
       <c r="H18">
-        <v>-0.28999999999999998</v>
+        <v>13.79</v>
       </c>
       <c r="I18">
-        <v>817.35</v>
+        <v>1818.16</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -8316,31 +7841,31 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B19">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="C19">
-        <v>517.86</v>
+        <v>965.01</v>
       </c>
       <c r="D19">
-        <v>293.74</v>
+        <v>771.31</v>
       </c>
       <c r="E19">
-        <v>11.81</v>
+        <v>33.92</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="G19">
-        <v>5.9</v>
+        <v>6.65</v>
       </c>
       <c r="H19">
-        <v>-0.06</v>
+        <v>11.36</v>
       </c>
       <c r="I19">
-        <v>845.01</v>
+        <v>1961.48</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -8357,31 +7882,31 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B20">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="C20">
-        <v>555.27</v>
+        <v>1049.42</v>
       </c>
       <c r="D20">
-        <v>322.23</v>
+        <v>801.69</v>
       </c>
       <c r="E20">
-        <v>12.39</v>
+        <v>34.5</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="G20">
-        <v>5.36</v>
+        <v>7.46</v>
       </c>
       <c r="H20">
-        <v>-0.06</v>
+        <v>10.62</v>
       </c>
       <c r="I20">
-        <v>909.5</v>
+        <v>2079.7199999999998</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -8393,539 +7918,6 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21">
-        <v>2010</v>
-      </c>
-      <c r="C21">
-        <v>585.41</v>
-      </c>
-      <c r="D21">
-        <v>349.52</v>
-      </c>
-      <c r="E21">
-        <v>13.32</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>5.61</v>
-      </c>
-      <c r="H21">
-        <v>-0.06</v>
-      </c>
-      <c r="I21">
-        <v>972.25</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>120</v>
-      </c>
-      <c r="B22">
-        <v>2011</v>
-      </c>
-      <c r="C22">
-        <v>636.4</v>
-      </c>
-      <c r="D22">
-        <v>378.48</v>
-      </c>
-      <c r="E22">
-        <v>14.21</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>5.25</v>
-      </c>
-      <c r="H22">
-        <v>-0.13</v>
-      </c>
-      <c r="I22">
-        <v>1059.1600000000001</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23">
-        <v>2012</v>
-      </c>
-      <c r="C23">
-        <v>662.84</v>
-      </c>
-      <c r="D23">
-        <v>407.44</v>
-      </c>
-      <c r="E23">
-        <v>14.1</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>4.79</v>
-      </c>
-      <c r="H23">
-        <v>-0.15</v>
-      </c>
-      <c r="I23">
-        <v>1114.54</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24">
-        <v>2013</v>
-      </c>
-      <c r="C24">
-        <v>698.03</v>
-      </c>
-      <c r="D24">
-        <v>430.77</v>
-      </c>
-      <c r="E24">
-        <v>15.54</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>5.6</v>
-      </c>
-      <c r="H24">
-        <v>-1.65</v>
-      </c>
-      <c r="I24">
-        <v>1182.42</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25">
-        <v>2014</v>
-      </c>
-      <c r="C25">
-        <v>748.32</v>
-      </c>
-      <c r="D25">
-        <v>478.19</v>
-      </c>
-      <c r="E25">
-        <v>16.18</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>5.01</v>
-      </c>
-      <c r="H25">
-        <v>-4.43</v>
-      </c>
-      <c r="I25">
-        <v>1288.45</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B26">
-        <v>2015</v>
-      </c>
-      <c r="C26">
-        <v>768.06</v>
-      </c>
-      <c r="D26">
-        <v>511.99</v>
-      </c>
-      <c r="E26">
-        <v>16.59</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>5.24</v>
-      </c>
-      <c r="H26">
-        <v>-5.15</v>
-      </c>
-      <c r="I26">
-        <v>1357.75</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27">
-        <v>2016</v>
-      </c>
-      <c r="C27">
-        <v>801.84</v>
-      </c>
-      <c r="D27">
-        <v>553.13</v>
-      </c>
-      <c r="E27">
-        <v>15.68</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>5.62</v>
-      </c>
-      <c r="H27">
-        <v>-6.71</v>
-      </c>
-      <c r="I27">
-        <v>1432.89</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>120</v>
-      </c>
-      <c r="B28">
-        <v>2017</v>
-      </c>
-      <c r="C28">
-        <v>850.93</v>
-      </c>
-      <c r="D28">
-        <v>583.78</v>
-      </c>
-      <c r="E28">
-        <v>17.43</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>5.07</v>
-      </c>
-      <c r="H28">
-        <v>-7.2</v>
-      </c>
-      <c r="I28">
-        <v>1510.1</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29">
-        <v>2018</v>
-      </c>
-      <c r="C29">
-        <v>918.63</v>
-      </c>
-      <c r="D29">
-        <v>615.14</v>
-      </c>
-      <c r="E29">
-        <v>18.84</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H29">
-        <v>-8.4700000000000006</v>
-      </c>
-      <c r="I29">
-        <v>1608.81</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30">
-        <v>2019</v>
-      </c>
-      <c r="C30">
-        <v>935.33</v>
-      </c>
-      <c r="D30">
-        <v>641.13</v>
-      </c>
-      <c r="E30">
-        <v>19.149999999999999</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>6.35</v>
-      </c>
-      <c r="H30">
-        <v>-9.49</v>
-      </c>
-      <c r="I30">
-        <v>1646.58</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31">
-        <v>2020</v>
-      </c>
-      <c r="C31">
-        <v>905.9</v>
-      </c>
-      <c r="D31">
-        <v>597.54</v>
-      </c>
-      <c r="E31">
-        <v>14.67</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="H31">
-        <v>-9.57</v>
-      </c>
-      <c r="I31">
-        <v>1536.76</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32">
-        <v>2021</v>
-      </c>
-      <c r="C32">
-        <v>960.02</v>
-      </c>
-      <c r="D32">
-        <v>665.35</v>
-      </c>
-      <c r="E32">
-        <v>21.93</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>7.97</v>
-      </c>
-      <c r="H32">
-        <v>-8.25</v>
-      </c>
-      <c r="I32">
-        <v>1636.31</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33">
-        <v>2022</v>
-      </c>
-      <c r="C33">
-        <v>1016.7</v>
-      </c>
-      <c r="D33">
-        <v>707.9</v>
-      </c>
-      <c r="E33">
-        <v>25</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33">
-        <v>7.84</v>
-      </c>
-      <c r="H33">
-        <v>-10.25</v>
-      </c>
-      <c r="I33">
-        <v>1814.06</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
         <v>0</v>
       </c>
     </row>
@@ -9000,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C11">
         <v>2020</v>
@@ -9041,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C12">
         <v>2025</v>
@@ -9082,7 +8074,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <v>2030</v>
@@ -9123,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C14">
         <v>2035</v>
@@ -9164,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C15">
         <v>2040</v>
@@ -9205,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C16">
         <v>2045</v>
@@ -9246,7 +8238,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C17">
         <v>2050</v>
@@ -9287,7 +8279,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C18">
         <v>2020</v>
@@ -9328,7 +8320,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C19">
         <v>2025</v>
@@ -9369,7 +8361,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C20">
         <v>2030</v>
@@ -9410,7 +8402,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C21">
         <v>2035</v>
@@ -9451,7 +8443,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C22">
         <v>2040</v>
@@ -9492,7 +8484,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C23">
         <v>2045</v>
@@ -9533,7 +8525,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C24">
         <v>2050</v>
@@ -9574,7 +8566,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C25">
         <v>2020</v>
@@ -9615,7 +8607,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C26">
         <v>2025</v>
@@ -9656,7 +8648,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C27">
         <v>2030</v>
@@ -9697,7 +8689,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C28">
         <v>2035</v>
@@ -9738,7 +8730,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C29">
         <v>2040</v>
@@ -9779,7 +8771,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C30">
         <v>2045</v>
@@ -9820,7 +8812,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C31">
         <v>2050</v>
@@ -9861,7 +8853,7 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C32">
         <v>2020</v>
@@ -9902,7 +8894,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C33">
         <v>2025</v>
@@ -9943,7 +8935,7 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C34">
         <v>2030</v>
@@ -9984,7 +8976,7 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C35">
         <v>2035</v>
@@ -10025,7 +9017,7 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C36">
         <v>2040</v>
@@ -10066,7 +9058,7 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C37">
         <v>2045</v>
@@ -10107,7 +9099,7 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C38">
         <v>2050</v>
@@ -10148,7 +9140,7 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C39">
         <v>2020</v>
@@ -10189,7 +9181,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C40">
         <v>2025</v>
@@ -10230,7 +9222,7 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C41">
         <v>2030</v>
@@ -10271,7 +9263,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C42">
         <v>2035</v>
@@ -10312,7 +9304,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C43">
         <v>2040</v>
@@ -10353,7 +9345,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C44">
         <v>2045</v>
@@ -10394,7 +9386,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C45">
         <v>2050</v>
@@ -10435,7 +9427,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C46">
         <v>2020</v>
@@ -10476,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C47">
         <v>2025</v>
@@ -10517,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C48">
         <v>2030</v>
@@ -10558,7 +9550,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C49">
         <v>2035</v>
@@ -10599,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C50">
         <v>2040</v>
@@ -10640,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C51">
         <v>2045</v>
@@ -10681,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C52">
         <v>2050</v>
@@ -10722,7 +9714,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C53">
         <v>2020</v>
@@ -10763,7 +9755,7 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C54">
         <v>2025</v>
@@ -10804,7 +9796,7 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C55">
         <v>2030</v>
@@ -10845,7 +9837,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C56">
         <v>2035</v>
@@ -10886,7 +9878,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C57">
         <v>2040</v>
@@ -10927,7 +9919,7 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C58">
         <v>2045</v>
@@ -10968,7 +9960,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C59">
         <v>2050</v>
@@ -11009,7 +10001,7 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C60">
         <v>2020</v>
@@ -11050,7 +10042,7 @@
         <v>5</v>
       </c>
       <c r="B61" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C61">
         <v>2025</v>
@@ -11091,7 +10083,7 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C62">
         <v>2030</v>
@@ -11132,7 +10124,7 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C63">
         <v>2035</v>
@@ -11173,7 +10165,7 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C64">
         <v>2040</v>
@@ -11214,7 +10206,7 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C65">
         <v>2045</v>
@@ -11255,7 +10247,7 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C66">
         <v>2050</v>
@@ -11296,7 +10288,7 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C67">
         <v>2020</v>
@@ -11337,7 +10329,7 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C68">
         <v>2025</v>
@@ -11378,7 +10370,7 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C69">
         <v>2030</v>
@@ -11419,7 +10411,7 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C70">
         <v>2035</v>
@@ -11460,7 +10452,7 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C71">
         <v>2040</v>
@@ -11501,7 +10493,7 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C72">
         <v>2045</v>
@@ -11542,7 +10534,7 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C73">
         <v>2050</v>
@@ -11583,7 +10575,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C74">
         <v>2020</v>
@@ -11624,7 +10616,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C75">
         <v>2025</v>
@@ -11665,7 +10657,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C76">
         <v>2030</v>
@@ -11706,7 +10698,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C77">
         <v>2035</v>
@@ -11747,7 +10739,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C78">
         <v>2040</v>
@@ -11788,7 +10780,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C79">
         <v>2045</v>
@@ -11829,7 +10821,7 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>2050</v>
@@ -11870,7 +10862,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>2020</v>
@@ -11911,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>2025</v>
@@ -11952,7 +10944,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>2030</v>
@@ -11993,7 +10985,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C84">
         <v>2035</v>
@@ -12034,7 +11026,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C85">
         <v>2040</v>
@@ -12075,7 +11067,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C86">
         <v>2045</v>
@@ -12116,7 +11108,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C87">
         <v>2050</v>
@@ -12157,7 +11149,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C88">
         <v>2020</v>
@@ -12198,7 +11190,7 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C89">
         <v>2025</v>
@@ -12239,7 +11231,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C90">
         <v>2030</v>
@@ -12280,7 +11272,7 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C91">
         <v>2035</v>
@@ -12321,7 +11313,7 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C92">
         <v>2040</v>
@@ -12362,7 +11354,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C93">
         <v>2045</v>
@@ -12403,7 +11395,7 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C94">
         <v>2050</v>
@@ -12444,7 +11436,7 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C95">
         <v>2020</v>
@@ -12485,7 +11477,7 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C96">
         <v>2025</v>
@@ -12526,7 +11518,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C97">
         <v>2030</v>
@@ -12567,7 +11559,7 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C98">
         <v>2035</v>
@@ -12608,7 +11600,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C99">
         <v>2040</v>
@@ -12649,7 +11641,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C100">
         <v>2045</v>
@@ -12690,7 +11682,7 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C101">
         <v>2050</v>
@@ -12731,7 +11723,7 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C102">
         <v>2020</v>
@@ -12772,7 +11764,7 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C103">
         <v>2025</v>
@@ -12813,7 +11805,7 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C104">
         <v>2030</v>
@@ -12854,7 +11846,7 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C105">
         <v>2035</v>
@@ -12895,7 +11887,7 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C106">
         <v>2040</v>
@@ -12936,7 +11928,7 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C107">
         <v>2045</v>
@@ -12977,7 +11969,7 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C108">
         <v>2050</v>
@@ -13018,7 +12010,7 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C109">
         <v>2020</v>
@@ -13059,7 +12051,7 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C110">
         <v>2025</v>
@@ -13100,7 +12092,7 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C111">
         <v>2030</v>
@@ -13141,7 +12133,7 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C112">
         <v>2035</v>
@@ -13182,7 +12174,7 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C113">
         <v>2040</v>
@@ -13223,7 +12215,7 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C114">
         <v>2045</v>
@@ -13264,7 +12256,7 @@
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C115">
         <v>2050</v>
@@ -13305,7 +12297,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C116">
         <v>2020</v>
@@ -13346,7 +12338,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C117">
         <v>2025</v>
@@ -13387,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C118">
         <v>2030</v>
@@ -13428,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C119">
         <v>2035</v>
@@ -13469,7 +12461,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C120">
         <v>2040</v>
@@ -13510,7 +12502,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C121">
         <v>2045</v>
@@ -13551,7 +12543,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C122">
         <v>2050</v>
@@ -13592,7 +12584,7 @@
         <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C123">
         <v>2020</v>
@@ -13633,7 +12625,7 @@
         <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C124">
         <v>2025</v>
@@ -13674,7 +12666,7 @@
         <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C125">
         <v>2030</v>
@@ -13715,7 +12707,7 @@
         <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C126">
         <v>2035</v>
@@ -13756,7 +12748,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C127">
         <v>2040</v>
@@ -13797,7 +12789,7 @@
         <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C128">
         <v>2045</v>
@@ -13838,7 +12830,7 @@
         <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C129">
         <v>2050</v>
@@ -13879,7 +12871,7 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C130">
         <v>2020</v>
@@ -13920,7 +12912,7 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C131">
         <v>2025</v>
@@ -13961,7 +12953,7 @@
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C132">
         <v>2030</v>
@@ -14002,7 +12994,7 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C133">
         <v>2035</v>
@@ -14043,7 +13035,7 @@
         <v>5</v>
       </c>
       <c r="B134" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C134">
         <v>2040</v>
@@ -14084,7 +13076,7 @@
         <v>5</v>
       </c>
       <c r="B135" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C135">
         <v>2045</v>
@@ -14125,7 +13117,7 @@
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C136">
         <v>2050</v>
@@ -14166,7 +13158,7 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C137">
         <v>2020</v>
@@ -14207,7 +13199,7 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C138">
         <v>2025</v>
@@ -14248,7 +13240,7 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C139">
         <v>2030</v>
@@ -14289,7 +13281,7 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C140">
         <v>2035</v>
@@ -14330,7 +13322,7 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C141">
         <v>2040</v>
@@ -14371,7 +13363,7 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C142">
         <v>2045</v>
@@ -14412,7 +13404,7 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C143">
         <v>2050</v>
@@ -14453,7 +13445,7 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C144">
         <v>2020</v>
@@ -14494,7 +13486,7 @@
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C145">
         <v>2025</v>
@@ -14535,7 +13527,7 @@
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C146">
         <v>2030</v>
@@ -14576,7 +13568,7 @@
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C147">
         <v>2035</v>
@@ -14617,7 +13609,7 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C148">
         <v>2040</v>
@@ -14658,7 +13650,7 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C149">
         <v>2045</v>
@@ -14699,7 +13691,7 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C150">
         <v>2050</v>
@@ -14740,7 +13732,7 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C151">
         <v>2020</v>
@@ -14781,7 +13773,7 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C152">
         <v>2025</v>
@@ -14822,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C153">
         <v>2030</v>
@@ -14863,7 +13855,7 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C154">
         <v>2035</v>
@@ -14904,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C155">
         <v>2040</v>
@@ -14945,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C156">
         <v>2045</v>
@@ -14986,7 +13978,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C157">
         <v>2050</v>
@@ -15027,7 +14019,7 @@
         <v>2</v>
       </c>
       <c r="B158" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C158">
         <v>2020</v>
@@ -15068,7 +14060,7 @@
         <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C159">
         <v>2025</v>
@@ -15109,7 +14101,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C160">
         <v>2030</v>
@@ -15150,7 +14142,7 @@
         <v>2</v>
       </c>
       <c r="B161" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C161">
         <v>2035</v>
@@ -15191,7 +14183,7 @@
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C162">
         <v>2040</v>
@@ -15232,7 +14224,7 @@
         <v>2</v>
       </c>
       <c r="B163" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C163">
         <v>2045</v>
@@ -15273,7 +14265,7 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C164">
         <v>2050</v>
@@ -15314,7 +14306,7 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C165">
         <v>2020</v>
@@ -15355,7 +14347,7 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C166">
         <v>2025</v>
@@ -15396,7 +14388,7 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C167">
         <v>2030</v>
@@ -15437,7 +14429,7 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C168">
         <v>2035</v>
@@ -15478,7 +14470,7 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C169">
         <v>2040</v>
@@ -15519,7 +14511,7 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C170">
         <v>2045</v>
@@ -15560,7 +14552,7 @@
         <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C171">
         <v>2050</v>
@@ -15601,7 +14593,7 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C172">
         <v>2020</v>
@@ -15642,7 +14634,7 @@
         <v>7</v>
       </c>
       <c r="B173" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C173">
         <v>2025</v>
@@ -15683,7 +14675,7 @@
         <v>7</v>
       </c>
       <c r="B174" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C174">
         <v>2030</v>
@@ -15724,7 +14716,7 @@
         <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C175">
         <v>2035</v>
@@ -15765,7 +14757,7 @@
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C176">
         <v>2040</v>
@@ -15806,7 +14798,7 @@
         <v>7</v>
       </c>
       <c r="B177" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C177">
         <v>2045</v>
@@ -15847,7 +14839,7 @@
         <v>7</v>
       </c>
       <c r="B178" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C178">
         <v>2050</v>
@@ -15888,7 +14880,7 @@
         <v>9</v>
       </c>
       <c r="B179" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C179">
         <v>2020</v>
@@ -15929,7 +14921,7 @@
         <v>9</v>
       </c>
       <c r="B180" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C180">
         <v>2025</v>
@@ -15970,7 +14962,7 @@
         <v>9</v>
       </c>
       <c r="B181" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C181">
         <v>2030</v>
@@ -16011,7 +15003,7 @@
         <v>9</v>
       </c>
       <c r="B182" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C182">
         <v>2035</v>
@@ -16052,7 +15044,7 @@
         <v>9</v>
       </c>
       <c r="B183" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C183">
         <v>2040</v>
@@ -16093,7 +15085,7 @@
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C184">
         <v>2045</v>
@@ -16134,7 +15126,7 @@
         <v>9</v>
       </c>
       <c r="B185" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C185">
         <v>2050</v>
@@ -16175,7 +15167,7 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C186">
         <v>2020</v>
@@ -16216,7 +15208,7 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C187">
         <v>2025</v>
@@ -16257,7 +15249,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C188">
         <v>2030</v>
@@ -16298,7 +15290,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C189">
         <v>2035</v>
@@ -16339,7 +15331,7 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C190">
         <v>2040</v>
@@ -16380,7 +15372,7 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C191">
         <v>2045</v>
@@ -16421,7 +15413,7 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C192">
         <v>2050</v>
@@ -16462,7 +15454,7 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C193">
         <v>2020</v>
@@ -16503,7 +15495,7 @@
         <v>2</v>
       </c>
       <c r="B194" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C194">
         <v>2025</v>
@@ -16544,7 +15536,7 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C195">
         <v>2030</v>
@@ -16585,7 +15577,7 @@
         <v>2</v>
       </c>
       <c r="B196" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C196">
         <v>2035</v>
@@ -16626,7 +15618,7 @@
         <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C197">
         <v>2040</v>
@@ -16667,7 +15659,7 @@
         <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C198">
         <v>2045</v>
@@ -16708,7 +15700,7 @@
         <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C199">
         <v>2050</v>
@@ -16749,7 +15741,7 @@
         <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C200">
         <v>2020</v>
@@ -16790,7 +15782,7 @@
         <v>5</v>
       </c>
       <c r="B201" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C201">
         <v>2025</v>
@@ -16831,7 +15823,7 @@
         <v>5</v>
       </c>
       <c r="B202" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C202">
         <v>2030</v>
@@ -16872,7 +15864,7 @@
         <v>5</v>
       </c>
       <c r="B203" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C203">
         <v>2035</v>
@@ -16913,7 +15905,7 @@
         <v>5</v>
       </c>
       <c r="B204" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C204">
         <v>2040</v>
@@ -16954,7 +15946,7 @@
         <v>5</v>
       </c>
       <c r="B205" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C205">
         <v>2045</v>
@@ -16995,7 +15987,7 @@
         <v>5</v>
       </c>
       <c r="B206" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C206">
         <v>2050</v>
@@ -17036,7 +16028,7 @@
         <v>7</v>
       </c>
       <c r="B207" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C207">
         <v>2020</v>
@@ -17077,7 +16069,7 @@
         <v>7</v>
       </c>
       <c r="B208" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C208">
         <v>2025</v>
@@ -17118,7 +16110,7 @@
         <v>7</v>
       </c>
       <c r="B209" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C209">
         <v>2030</v>
@@ -17159,7 +16151,7 @@
         <v>7</v>
       </c>
       <c r="B210" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C210">
         <v>2035</v>
@@ -17200,7 +16192,7 @@
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C211">
         <v>2040</v>
@@ -17241,7 +16233,7 @@
         <v>7</v>
       </c>
       <c r="B212" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C212">
         <v>2045</v>
@@ -17282,7 +16274,7 @@
         <v>7</v>
       </c>
       <c r="B213" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C213">
         <v>2050</v>
@@ -17323,7 +16315,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C214">
         <v>2020</v>
@@ -17364,7 +16356,7 @@
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C215">
         <v>2025</v>
@@ -17405,7 +16397,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C216">
         <v>2030</v>
@@ -17446,7 +16438,7 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C217">
         <v>2035</v>
@@ -17487,7 +16479,7 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C218">
         <v>2040</v>
@@ -17528,7 +16520,7 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C219">
         <v>2045</v>
@@ -17569,7 +16561,7 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C220">
         <v>2050</v>
@@ -17610,7 +16602,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C221">
         <v>2020</v>
@@ -17651,7 +16643,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C222">
         <v>2025</v>
@@ -17692,7 +16684,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C223">
         <v>2030</v>
@@ -17733,7 +16725,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C224">
         <v>2035</v>
@@ -17774,7 +16766,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C225">
         <v>2040</v>
@@ -17815,7 +16807,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C226">
         <v>2045</v>
@@ -17856,7 +16848,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C227">
         <v>2050</v>
@@ -17897,7 +16889,7 @@
         <v>2</v>
       </c>
       <c r="B228" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C228">
         <v>2020</v>
@@ -17938,7 +16930,7 @@
         <v>2</v>
       </c>
       <c r="B229" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C229">
         <v>2025</v>
@@ -17979,7 +16971,7 @@
         <v>2</v>
       </c>
       <c r="B230" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C230">
         <v>2030</v>
@@ -18020,7 +17012,7 @@
         <v>2</v>
       </c>
       <c r="B231" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C231">
         <v>2035</v>
@@ -18061,7 +17053,7 @@
         <v>2</v>
       </c>
       <c r="B232" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C232">
         <v>2040</v>
@@ -18102,7 +17094,7 @@
         <v>2</v>
       </c>
       <c r="B233" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C233">
         <v>2045</v>
@@ -18143,7 +17135,7 @@
         <v>2</v>
       </c>
       <c r="B234" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C234">
         <v>2050</v>
@@ -18184,7 +17176,7 @@
         <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C235">
         <v>2020</v>
@@ -18225,7 +17217,7 @@
         <v>5</v>
       </c>
       <c r="B236" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C236">
         <v>2025</v>
@@ -18266,7 +17258,7 @@
         <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C237">
         <v>2030</v>
@@ -18307,7 +17299,7 @@
         <v>5</v>
       </c>
       <c r="B238" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C238">
         <v>2035</v>
@@ -18348,7 +17340,7 @@
         <v>5</v>
       </c>
       <c r="B239" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C239">
         <v>2040</v>
@@ -18389,7 +17381,7 @@
         <v>5</v>
       </c>
       <c r="B240" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C240">
         <v>2045</v>
@@ -18430,7 +17422,7 @@
         <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C241">
         <v>2050</v>
@@ -18471,7 +17463,7 @@
         <v>7</v>
       </c>
       <c r="B242" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C242">
         <v>2020</v>
@@ -18512,7 +17504,7 @@
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C243">
         <v>2025</v>
@@ -18553,7 +17545,7 @@
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C244">
         <v>2030</v>
@@ -18594,7 +17586,7 @@
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C245">
         <v>2035</v>
@@ -18635,7 +17627,7 @@
         <v>7</v>
       </c>
       <c r="B246" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C246">
         <v>2040</v>
@@ -18676,7 +17668,7 @@
         <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C247">
         <v>2045</v>
@@ -18717,7 +17709,7 @@
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C248">
         <v>2050</v>
@@ -18758,7 +17750,7 @@
         <v>9</v>
       </c>
       <c r="B249" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C249">
         <v>2020</v>
@@ -18799,7 +17791,7 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C250">
         <v>2025</v>
@@ -18840,7 +17832,7 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C251">
         <v>2030</v>
@@ -18881,7 +17873,7 @@
         <v>9</v>
       </c>
       <c r="B252" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C252">
         <v>2035</v>
@@ -18922,7 +17914,7 @@
         <v>9</v>
       </c>
       <c r="B253" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C253">
         <v>2040</v>
@@ -18963,7 +17955,7 @@
         <v>9</v>
       </c>
       <c r="B254" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C254">
         <v>2045</v>
@@ -19004,7 +17996,7 @@
         <v>9</v>
       </c>
       <c r="B255" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C255">
         <v>2050</v>
@@ -19045,7 +18037,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C256">
         <v>2020</v>
@@ -19086,7 +18078,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C257">
         <v>2025</v>
@@ -19127,7 +18119,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C258">
         <v>2030</v>
@@ -19168,7 +18160,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C259">
         <v>2035</v>
@@ -19209,7 +18201,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C260">
         <v>2040</v>
@@ -19250,7 +18242,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C261">
         <v>2045</v>
@@ -19291,7 +18283,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C262">
         <v>2050</v>
@@ -19332,7 +18324,7 @@
         <v>2</v>
       </c>
       <c r="B263" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C263">
         <v>2020</v>
@@ -19373,7 +18365,7 @@
         <v>2</v>
       </c>
       <c r="B264" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C264">
         <v>2025</v>
@@ -19414,7 +18406,7 @@
         <v>2</v>
       </c>
       <c r="B265" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C265">
         <v>2030</v>
@@ -19455,7 +18447,7 @@
         <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C266">
         <v>2035</v>
@@ -19496,7 +18488,7 @@
         <v>2</v>
       </c>
       <c r="B267" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C267">
         <v>2040</v>
@@ -19537,7 +18529,7 @@
         <v>2</v>
       </c>
       <c r="B268" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C268">
         <v>2045</v>
@@ -19578,7 +18570,7 @@
         <v>2</v>
       </c>
       <c r="B269" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C269">
         <v>2050</v>
@@ -19619,7 +18611,7 @@
         <v>5</v>
       </c>
       <c r="B270" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C270">
         <v>2020</v>
@@ -19660,7 +18652,7 @@
         <v>5</v>
       </c>
       <c r="B271" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C271">
         <v>2025</v>
@@ -19701,7 +18693,7 @@
         <v>5</v>
       </c>
       <c r="B272" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C272">
         <v>2030</v>
@@ -19742,7 +18734,7 @@
         <v>5</v>
       </c>
       <c r="B273" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C273">
         <v>2035</v>
@@ -19783,7 +18775,7 @@
         <v>5</v>
       </c>
       <c r="B274" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C274">
         <v>2040</v>
@@ -19824,7 +18816,7 @@
         <v>5</v>
       </c>
       <c r="B275" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C275">
         <v>2045</v>
@@ -19865,7 +18857,7 @@
         <v>5</v>
       </c>
       <c r="B276" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C276">
         <v>2050</v>
@@ -19906,7 +18898,7 @@
         <v>7</v>
       </c>
       <c r="B277" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C277">
         <v>2020</v>
@@ -19947,7 +18939,7 @@
         <v>7</v>
       </c>
       <c r="B278" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C278">
         <v>2025</v>
@@ -19988,7 +18980,7 @@
         <v>7</v>
       </c>
       <c r="B279" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C279">
         <v>2030</v>
@@ -20029,7 +19021,7 @@
         <v>7</v>
       </c>
       <c r="B280" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C280">
         <v>2035</v>
@@ -20070,7 +19062,7 @@
         <v>7</v>
       </c>
       <c r="B281" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C281">
         <v>2040</v>
@@ -20111,7 +19103,7 @@
         <v>7</v>
       </c>
       <c r="B282" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C282">
         <v>2045</v>
@@ -20152,7 +19144,7 @@
         <v>7</v>
       </c>
       <c r="B283" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C283">
         <v>2050</v>
@@ -20193,7 +19185,7 @@
         <v>9</v>
       </c>
       <c r="B284" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C284">
         <v>2020</v>
@@ -20234,7 +19226,7 @@
         <v>9</v>
       </c>
       <c r="B285" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C285">
         <v>2025</v>
@@ -20275,7 +19267,7 @@
         <v>9</v>
       </c>
       <c r="B286" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C286">
         <v>2030</v>
@@ -20316,7 +19308,7 @@
         <v>9</v>
       </c>
       <c r="B287" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C287">
         <v>2035</v>
@@ -20357,7 +19349,7 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C288">
         <v>2040</v>
@@ -20398,7 +19390,7 @@
         <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C289">
         <v>2045</v>
@@ -20439,7 +19431,7 @@
         <v>9</v>
       </c>
       <c r="B290" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C290">
         <v>2050</v>
@@ -20480,7 +19472,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C291">
         <v>2020</v>
@@ -20521,7 +19513,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C292">
         <v>2025</v>
@@ -20562,7 +19554,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C293">
         <v>2030</v>
@@ -20603,7 +19595,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C294">
         <v>2035</v>
@@ -20644,7 +19636,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C295">
         <v>2040</v>
@@ -20685,7 +19677,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C296">
         <v>2045</v>
@@ -20726,7 +19718,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C297">
         <v>2050</v>
@@ -20767,7 +19759,7 @@
         <v>2</v>
       </c>
       <c r="B298" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C298">
         <v>2020</v>
@@ -20808,7 +19800,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C299">
         <v>2025</v>
@@ -20849,7 +19841,7 @@
         <v>2</v>
       </c>
       <c r="B300" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C300">
         <v>2030</v>
@@ -20890,7 +19882,7 @@
         <v>2</v>
       </c>
       <c r="B301" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C301">
         <v>2035</v>
@@ -20931,7 +19923,7 @@
         <v>2</v>
       </c>
       <c r="B302" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C302">
         <v>2040</v>
@@ -20972,7 +19964,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C303">
         <v>2045</v>
@@ -21013,7 +20005,7 @@
         <v>2</v>
       </c>
       <c r="B304" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C304">
         <v>2050</v>
@@ -21054,7 +20046,7 @@
         <v>5</v>
       </c>
       <c r="B305" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C305">
         <v>2020</v>
@@ -21095,7 +20087,7 @@
         <v>5</v>
       </c>
       <c r="B306" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C306">
         <v>2025</v>
@@ -21136,7 +20128,7 @@
         <v>5</v>
       </c>
       <c r="B307" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C307">
         <v>2030</v>
@@ -21177,7 +20169,7 @@
         <v>5</v>
       </c>
       <c r="B308" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C308">
         <v>2035</v>
@@ -21218,7 +20210,7 @@
         <v>5</v>
       </c>
       <c r="B309" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C309">
         <v>2040</v>
@@ -21259,7 +20251,7 @@
         <v>5</v>
       </c>
       <c r="B310" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C310">
         <v>2045</v>
@@ -21300,7 +20292,7 @@
         <v>5</v>
       </c>
       <c r="B311" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C311">
         <v>2050</v>
@@ -21341,7 +20333,7 @@
         <v>7</v>
       </c>
       <c r="B312" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C312">
         <v>2020</v>
@@ -21382,7 +20374,7 @@
         <v>7</v>
       </c>
       <c r="B313" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C313">
         <v>2025</v>
@@ -21423,7 +20415,7 @@
         <v>7</v>
       </c>
       <c r="B314" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C314">
         <v>2030</v>
@@ -21464,7 +20456,7 @@
         <v>7</v>
       </c>
       <c r="B315" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C315">
         <v>2035</v>
@@ -21505,7 +20497,7 @@
         <v>7</v>
       </c>
       <c r="B316" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C316">
         <v>2040</v>
@@ -21546,7 +20538,7 @@
         <v>7</v>
       </c>
       <c r="B317" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C317">
         <v>2045</v>
@@ -21587,7 +20579,7 @@
         <v>7</v>
       </c>
       <c r="B318" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C318">
         <v>2050</v>
@@ -21628,7 +20620,7 @@
         <v>9</v>
       </c>
       <c r="B319" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C319">
         <v>2020</v>
@@ -21669,7 +20661,7 @@
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C320">
         <v>2025</v>
@@ -21710,7 +20702,7 @@
         <v>9</v>
       </c>
       <c r="B321" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C321">
         <v>2030</v>
@@ -21751,7 +20743,7 @@
         <v>9</v>
       </c>
       <c r="B322" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C322">
         <v>2035</v>
@@ -21792,7 +20784,7 @@
         <v>9</v>
       </c>
       <c r="B323" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C323">
         <v>2040</v>
@@ -21833,7 +20825,7 @@
         <v>9</v>
       </c>
       <c r="B324" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C324">
         <v>2045</v>
@@ -21874,7 +20866,7 @@
         <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C325">
         <v>2050</v>
@@ -21915,7 +20907,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C326">
         <v>2020</v>
@@ -21956,7 +20948,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C327">
         <v>2025</v>
@@ -21997,7 +20989,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C328">
         <v>2030</v>
@@ -22038,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C329">
         <v>2035</v>
@@ -22079,7 +21071,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C330">
         <v>2040</v>
@@ -22120,7 +21112,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C331">
         <v>2045</v>
@@ -22161,7 +21153,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C332">
         <v>2050</v>
@@ -22202,7 +21194,7 @@
         <v>2</v>
       </c>
       <c r="B333" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C333">
         <v>2020</v>
@@ -22243,7 +21235,7 @@
         <v>2</v>
       </c>
       <c r="B334" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C334">
         <v>2025</v>
@@ -22284,7 +21276,7 @@
         <v>2</v>
       </c>
       <c r="B335" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C335">
         <v>2030</v>
@@ -22325,7 +21317,7 @@
         <v>2</v>
       </c>
       <c r="B336" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C336">
         <v>2035</v>
@@ -22366,7 +21358,7 @@
         <v>2</v>
       </c>
       <c r="B337" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C337">
         <v>2040</v>
@@ -22407,7 +21399,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C338">
         <v>2045</v>
@@ -22448,7 +21440,7 @@
         <v>2</v>
       </c>
       <c r="B339" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C339">
         <v>2050</v>
@@ -22489,7 +21481,7 @@
         <v>5</v>
       </c>
       <c r="B340" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C340">
         <v>2020</v>
@@ -22530,7 +21522,7 @@
         <v>5</v>
       </c>
       <c r="B341" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C341">
         <v>2025</v>
@@ -22571,7 +21563,7 @@
         <v>5</v>
       </c>
       <c r="B342" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C342">
         <v>2030</v>
@@ -22612,7 +21604,7 @@
         <v>5</v>
       </c>
       <c r="B343" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C343">
         <v>2035</v>
@@ -22653,7 +21645,7 @@
         <v>5</v>
       </c>
       <c r="B344" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C344">
         <v>2040</v>
@@ -22694,7 +21686,7 @@
         <v>5</v>
       </c>
       <c r="B345" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C345">
         <v>2045</v>
@@ -22735,7 +21727,7 @@
         <v>5</v>
       </c>
       <c r="B346" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C346">
         <v>2050</v>
@@ -22776,7 +21768,7 @@
         <v>7</v>
       </c>
       <c r="B347" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C347">
         <v>2020</v>
@@ -22817,7 +21809,7 @@
         <v>7</v>
       </c>
       <c r="B348" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C348">
         <v>2025</v>
@@ -22858,7 +21850,7 @@
         <v>7</v>
       </c>
       <c r="B349" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C349">
         <v>2030</v>
@@ -22899,7 +21891,7 @@
         <v>7</v>
       </c>
       <c r="B350" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C350">
         <v>2035</v>
@@ -22940,7 +21932,7 @@
         <v>7</v>
       </c>
       <c r="B351" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C351">
         <v>2040</v>
@@ -22981,7 +21973,7 @@
         <v>7</v>
       </c>
       <c r="B352" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C352">
         <v>2045</v>
@@ -23022,7 +22014,7 @@
         <v>7</v>
       </c>
       <c r="B353" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C353">
         <v>2050</v>
@@ -23063,7 +22055,7 @@
         <v>9</v>
       </c>
       <c r="B354" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C354">
         <v>2020</v>
@@ -23104,7 +22096,7 @@
         <v>9</v>
       </c>
       <c r="B355" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C355">
         <v>2025</v>
@@ -23145,7 +22137,7 @@
         <v>9</v>
       </c>
       <c r="B356" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C356">
         <v>2030</v>
@@ -23186,7 +22178,7 @@
         <v>9</v>
       </c>
       <c r="B357" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C357">
         <v>2035</v>
@@ -23227,7 +22219,7 @@
         <v>9</v>
       </c>
       <c r="B358" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C358">
         <v>2040</v>
@@ -23268,7 +22260,7 @@
         <v>9</v>
       </c>
       <c r="B359" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C359">
         <v>2045</v>
@@ -23309,7 +22301,7 @@
         <v>9</v>
       </c>
       <c r="B360" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="C360">
         <v>2050</v>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A85491D-413A-46CB-A2B0-D6050C3133F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBA5EB4-966D-46A8-B4C7-6DAAFC8AAB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan10/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBA5EB4-966D-46A8-B4C7-6DAAFC8AAB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BE50BC-94EF-48DB-9727-578A1AD58DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
